--- a/artfynd/A 57277-2024 artfynd.xlsx
+++ b/artfynd/A 57277-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120441920</v>
+        <v>120441897</v>
       </c>
       <c r="B2" t="n">
-        <v>95350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491731</v>
+        <v>491653</v>
       </c>
       <c r="R2" t="n">
-        <v>6664298</v>
+        <v>6664333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120441897</v>
+        <v>120441775</v>
       </c>
       <c r="B3" t="n">
-        <v>78239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491653</v>
+        <v>491798</v>
       </c>
       <c r="R3" t="n">
-        <v>6664333</v>
+        <v>6664342</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120441824</v>
+        <v>120441812</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491543</v>
+        <v>491518</v>
       </c>
       <c r="R4" t="n">
-        <v>6664398</v>
+        <v>6664329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120441926</v>
+        <v>120441920</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491791</v>
+        <v>491731</v>
       </c>
       <c r="R5" t="n">
-        <v>6664314</v>
+        <v>6664298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120441839</v>
+        <v>120441824</v>
       </c>
       <c r="B6" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491786</v>
+        <v>491543</v>
       </c>
       <c r="R6" t="n">
-        <v>6664338</v>
+        <v>6664398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120441812</v>
+        <v>120441825</v>
       </c>
       <c r="B7" t="n">
-        <v>91971</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491518</v>
+        <v>491677</v>
       </c>
       <c r="R7" t="n">
-        <v>6664329</v>
+        <v>6664297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120441838</v>
+        <v>120441898</v>
       </c>
       <c r="B8" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491749</v>
+        <v>491532</v>
       </c>
       <c r="R8" t="n">
-        <v>6664315</v>
+        <v>6664330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,16 +1357,11 @@
         <v>120441899</v>
       </c>
       <c r="B9" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120441898</v>
+        <v>120441813</v>
       </c>
       <c r="B10" t="n">
-        <v>91955</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491532</v>
+        <v>491561</v>
       </c>
       <c r="R10" t="n">
-        <v>6664330</v>
+        <v>6664323</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120441775</v>
+        <v>120441868</v>
       </c>
       <c r="B11" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491798</v>
+        <v>491794</v>
       </c>
       <c r="R11" t="n">
-        <v>6664342</v>
+        <v>6664283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120441825</v>
+        <v>120441827</v>
       </c>
       <c r="B12" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491677</v>
+        <v>491658</v>
       </c>
       <c r="R12" t="n">
-        <v>6664297</v>
+        <v>6664316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120441827</v>
+        <v>120441926</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491658</v>
+        <v>491791</v>
       </c>
       <c r="R13" t="n">
-        <v>6664316</v>
+        <v>6664314</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120441868</v>
+        <v>120441838</v>
       </c>
       <c r="B14" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491794</v>
+        <v>491749</v>
       </c>
       <c r="R14" t="n">
-        <v>6664283</v>
+        <v>6664315</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120441813</v>
+        <v>120441839</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491561</v>
+        <v>491786</v>
       </c>
       <c r="R15" t="n">
-        <v>6664323</v>
+        <v>6664338</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
